--- a/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
+++ b/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day Plan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task Tracker" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DQ Matrix" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Learning Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Day Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Task Tracker" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DQ Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Metrics" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Learning Log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Task Tracker'!$A$4:$H$74</definedName>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr"/>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr"/>
@@ -1560,10 +1560,14 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>Row counts in Metrics 1-5. profile.py replaces the ad-hoc loop.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -1596,10 +1600,14 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>8 cohort codes; 72 patients have a complication but no T2DM code. See cohort.py.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -1632,10 +1640,14 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Units are %, so DQ3 order of magnitude OK — but floor 3.0 flags 993 clean values.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -1668,10 +1680,14 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>0.0% resolved → D5 decided early, no active-as-of filter needed.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -3829,7 +3845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3918,8 +3934,16 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>1,000 (-p 1000) → 1,142 patient records</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Synthea -p counts survivors, so 1,000 alive + 142 deceased. Keeps every query sub-second while still yielding a 161-patient cohort. Deceased are loaded but excluded from the gap denominator on Day 4.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="74" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3947,8 +3971,16 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr"/>
-      <c r="G6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Massachusetts, seed 20260823</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>The seed is the half that matters — it makes every README number reproducible by a reviewer. MA is Synthea's best-calibrated state. Note --exporter.fhir.export false alone is not enough; hospital and practitioner FHIR need their own flags.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="74" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -4034,8 +4066,16 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr"/>
-      <c r="G9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Any of 8 diabetes SNOMED codes ever recorded. No active-as-of filter. Cohort = 161.</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Decided Day 1 — the evidence arrived early. Anchoring on 44054006 alone misses 72 patients who carry a diabetic complication with no underlying dx code (45% of cohort, and the sickest half). Prediabetes 714628002 excluded: 430 patients, would triple the denominator. 0 of 819 diabetes rows have a stop date, so "ever recorded" needs no date logic. See pipeline/cohort.py.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="74" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -4239,6 +4279,117 @@
       </c>
       <c r="F16" s="13" t="inlineStr"/>
       <c r="G16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="74" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Which lab defines the care gap — A1c or blood glucose</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Glucose is the larger table (9,879 vs 8,749) and covers more of the cohort. Both are reasons to reject it.</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Choosing glucose would silently break the claim that this implements a real published measure.</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>HbA1c, LOINC 4548-4. Glucose (2339-0, 2345-7) is context only, never a gap definition.</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>A1c integrates ~3 months of blood sugar; glucose is a snapshot. In our own data the within-patient, within-year spread is 6.2% of the mean for A1c vs 21.0% for glucose. Glucose is also drawn on everyone incidentally — 160 of 161 cohort patients have one vs 131 with an A1c — so its absence carries no signal. And HEDIS specifies A1c; no measure anywhere requires an annual glucose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="74" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Synthea export format — CSV or FHIR</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>FHIR JSON is more realistic interchange; CSV loads in one line of DuckDB.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Determines how much of the seven days is spent parsing versus on the actual subject.</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>CSV (--exporter.csv.export true, all three FHIR exporters false)</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>FHIR conformance is an explicit PRD non-goal. The subject of this project is data quality, not nested resource parsing. CSV spends the time on the subject.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="74" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Which of the 18 Synthea CSVs get loaded into Bronze</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>All 18 (773 MB), or the five the care gap actually needs.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>claims_transactions alone is 1,031,224 rows — 40% of total volume with no clinical role.</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Five: patients, encounters, conditions, observations, medications.</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Everything else is billing (claims, payers), or clinical data with no bearing on an A1c gap (imaging_studies, procedures, devices, supplies, allergies, careplans, immunizations). organizations/providers may be added on Day 6 if role views need facility names.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4704,7 +4855,9 @@
           <t>Bronze rows — patients</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr"/>
+      <c r="C5" s="12" t="n">
+        <v>1142</v>
+      </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
           <t>README architecture table, P2 layer counts</t>
@@ -4725,7 +4878,9 @@
           <t>Bronze rows — encounters</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr"/>
+      <c r="C6" s="12" t="n">
+        <v>65350</v>
+      </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
           <t>README architecture table, P2 layer counts</t>
@@ -4746,7 +4901,9 @@
           <t>Bronze rows — conditions</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr"/>
+      <c r="C7" s="12" t="n">
+        <v>40105</v>
+      </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
           <t>README architecture table, P2 layer counts</t>
@@ -4767,7 +4924,9 @@
           <t>Bronze rows — observations</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
+      <c r="C8" s="12" t="n">
+        <v>836111</v>
+      </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
           <t>README architecture table, P2 layer counts</t>
@@ -4788,7 +4947,9 @@
           <t>Bronze rows — medications</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
+      <c r="C9" s="12" t="n">
+        <v>56228</v>
+      </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
           <t>README architecture table, P2 layer counts</t>
@@ -4809,7 +4970,11 @@
           <t>Distinct diabetes SNOMED codes found</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>8 in cohort (9 matched "%diabet%"; prediabetes 714628002 excluded)</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
           <t>DATA_DICTIONARY.md code table</t>
@@ -4830,7 +4995,11 @@
           <t>A1c LOINC code confirmed</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>4548-4 — Hemoglobin A1c/Hemoglobin.total in Blood, units "%"</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
           <t>DATA_DICTIONARY.md code table</t>
@@ -4851,7 +5020,11 @@
           <t>A1c value range (min / median / max)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>2.3 / 5.2 / 8.8  (n=8,749; 993 below DQ3 floor of 3.0 → revise floor to 2.0)</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Sanity check for DQ3's 3.0-20.0 bounds</t>
@@ -4872,7 +5045,11 @@
           <t>% of diabetes conditions with a resolved_date</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>0.0%  (0 of 819 diabetes condition rows have a STOP date)</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Decides cohort definition D5</t>
@@ -5019,7 +5196,9 @@
           <t>Diabetic patients in cohort (denominator)</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr"/>
+      <c r="C20" s="12" t="n">
+        <v>161</v>
+      </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
           <t>README result line, P1 headline</t>
@@ -5082,7 +5261,9 @@
           <t>Patients never tested for A1c</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr"/>
+      <c r="C23" s="12" t="n">
+        <v>30</v>
+      </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
           <t>P3 — the highest-risk subgroup</t>
@@ -5090,7 +5271,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Day 4</t>
+          <t>Day 1</t>
         </is>
       </c>
     </row>

--- a/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
+++ b/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
@@ -1491,7 +1491,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>V1.3 failed with -s alone (data grew 4-6% four weeks later). Fixed with -cs -r -e; regenerated 2026-09-20. Full command in DAY_1_DECISIONS.md D2.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>8 cohort codes; 72 patients have a complication but no T2DM code. See cohort.py.</t>
+          <t>8 cohort codes; 73 patients have a complication but no T2DM code. See cohort.py.</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1649,7 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>Units are %, so DQ3 order of magnitude OK — but floor 3.0 flags 993 clean values.</t>
+          <t>Units are %, so DQ3 order of magnitude OK — but floor 3.0 flags 951 clean values.</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3940,12 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>1,000 (-p 1000) → 1,142 patient records</t>
+          <t>1,000 (-p 1000) → 1,153 patient records</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Synthea -p counts survivors, so 1,000 alive + 142 deceased. Keeps every query sub-second while still yielding a 161-patient cohort. Deceased are loaded but excluded from the gap denominator on Day 4.</t>
+          <t>Synthea -p counts survivors, so 1,000 alive + 153 deceased. Keeps every query sub-second while still yielding a 161-patient cohort. Deceased are loaded but excluded from the gap denominator on Day 4.</t>
         </is>
       </c>
     </row>
@@ -3973,12 +3977,12 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Massachusetts, seed 20260823</t>
+          <t>Massachusetts; -s 20260823 -cs 20260823 -r 20260823 -e 20260823</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>The seed is the half that matters — it makes every README number reproducible by a reviewer. MA is Synthea's best-calibrated state. Note --exporter.fhir.export false alone is not enough; hospital and practitioner FHIR need their own flags.</t>
+          <t>V1.3 FAILED on the Day 1 command (-s only): four weeks later the same seed gave 1,151 patients, not 1,142. -s pins the patient RNG but the clinician seed (-cs), reference date (-r) and end date (-e) all default to the wall clock. Each was found by fixing one and seeing what still moved. With all four, two runs are identical in content. Data regenerated 2026-09-20; every number here is from the pinned output. See DAY_1_DECISIONS.md D2.</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4077,7 @@
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Decided Day 1 — the evidence arrived early. Anchoring on 44054006 alone misses 72 patients who carry a diabetic complication with no underlying dx code (45% of cohort, and the sickest half). Prediabetes 714628002 excluded: 430 patients, would triple the denominator. 0 of 819 diabetes rows have a stop date, so "ever recorded" needs no date logic. See pipeline/cohort.py.</t>
+          <t>Decided Day 1 — the evidence arrived early. Anchoring on 44054006 alone misses 73 patients who carry a diabetic complication with no underlying dx code (45% of cohort, and the sickest half). Prediabetes 714628002 excluded: 439 patients, would triple the denominator. 0 of 835 diabetes rows have a stop date, so "ever recorded" needs no date logic. See pipeline/cohort.py.</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4297,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Glucose is the larger table (9,879 vs 8,749) and covers more of the cohort. Both are reasons to reject it.</t>
+          <t>Glucose is the larger table (10,439 vs 8,941) and covers more of the cohort. Both are reasons to reject it.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -4313,7 +4317,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>A1c integrates ~3 months of blood sugar; glucose is a snapshot. In our own data the within-patient, within-year spread is 6.2% of the mean for A1c vs 21.0% for glucose. Glucose is also drawn on everyone incidentally — 160 of 161 cohort patients have one vs 131 with an A1c — so its absence carries no signal. And HEDIS specifies A1c; no measure anywhere requires an annual glucose.</t>
+          <t>A1c integrates ~3 months of blood sugar; glucose is a snapshot. In our own data the within-patient, within-year spread is 6.7% of the mean for A1c vs 21.3% for glucose. Glucose is also drawn on everyone incidentally — 159 of 161 cohort patients have one vs 133 with an A1c — so its absence carries no signal. And HEDIS specifies A1c; no measure anywhere requires an annual glucose.</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4376,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>claims_transactions alone is 1,031,224 rows — 40% of total volume with no clinical role.</t>
+          <t>claims_transactions alone is 1,094,500 rows — 40% of total volume with no clinical role.</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -4856,7 +4860,7 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
@@ -4879,7 +4883,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>65350</v>
+        <v>67755</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
@@ -4902,7 +4906,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>40105</v>
+        <v>40811</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
@@ -4925,7 +4929,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>836111</v>
+        <v>870510</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
@@ -4948,7 +4952,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>56228</v>
+        <v>59273</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
@@ -5022,7 +5026,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2.3 / 5.2 / 8.8  (n=8,749; 993 below DQ3 floor of 3.0 → revise floor to 2.0)</t>
+          <t>2.3 / 4.1 / 8.8  (n=8,941; 951 below DQ3 floor of 3.0 → revise floor to 2.0)</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -5047,7 +5051,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>0.0%  (0 of 819 diabetes condition rows have a STOP date)</t>
+          <t>0.0%  (0 of 835 diabetes condition rows have a STOP date)</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -5262,7 +5266,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>

--- a/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
+++ b/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr"/>
@@ -1832,10 +1832,14 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>D3 recorded: 40/150/20/8/25/6 = 249 rows, all under 1% of table.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="62" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -1868,7 +1872,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr"/>
@@ -1904,7 +1908,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr"/>
@@ -1940,7 +1944,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr"/>
@@ -1976,7 +1980,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr"/>
@@ -2012,7 +2016,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr"/>
@@ -2048,7 +2052,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr"/>
@@ -2084,10 +2088,14 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>data/injected_defects.json - 249 entries, no timestamps so V2.3 can diff it. Committed.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
@@ -2120,10 +2128,14 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Reload-first: corrupt.py calls load_bronze before injecting. V2.3 + V2.4 pass; JSON byte-identical across runs.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="62" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -4012,8 +4024,16 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr"/>
-      <c r="G7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>D1 40 · D2 150 · D3 20 · D4 8 · D5 25 · D6 6  (≈249 rows)</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Nothing exceeds 1% of its table (largest is D4 at 0.7% of patients). Enough that quarantine reads as a real work queue on P2, small enough that the 161-patient cohort and its 133 A1c-tested patients survive (V2.7). D3 rows are sampled from cohort patients so Decision D4 (remediate vs quarantine) visibly moves the gap count on Day 4.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="74" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -4511,7 +4531,9 @@
           <t>DQ1 — encounter uniqueness</t>
         </is>
       </c>
-      <c r="F5" s="12" t="n"/>
+      <c r="F5" s="12" t="n">
+        <v>40</v>
+      </c>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="8">
         <f>IF(COUNT(G5)=0,"",IF(G5&gt;0,"YES","NO"))</f>
@@ -4545,7 +4567,9 @@
           <t>DQ2 — referential integrity</t>
         </is>
       </c>
-      <c r="F6" s="12" t="n"/>
+      <c r="F6" s="12" t="n">
+        <v>150</v>
+      </c>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="8">
         <f>IF(COUNT(G6)=0,"",IF(G6&gt;0,"YES","NO"))</f>
@@ -4579,7 +4603,9 @@
           <t>DQ3 — A1c plausibility</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
+      <c r="F7" s="12" t="n">
+        <v>20</v>
+      </c>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="8">
         <f>IF(COUNT(G7)=0,"",IF(G7&gt;0,"YES","NO"))</f>
@@ -4613,7 +4639,9 @@
           <t>DQ4 — birth date sanity</t>
         </is>
       </c>
-      <c r="F8" s="12" t="n"/>
+      <c r="F8" s="12" t="n">
+        <v>8</v>
+      </c>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="8">
         <f>IF(COUNT(G8)=0,"",IF(G8&gt;0,"YES","NO"))</f>
@@ -4647,7 +4675,9 @@
           <t>DQ5 — encounter chronology</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
+      <c r="F9" s="12" t="n">
+        <v>25</v>
+      </c>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="8">
         <f>IF(COUNT(G9)=0,"",IF(G9&gt;0,"YES","NO"))</f>
@@ -4681,7 +4711,9 @@
           <t>DQ6 — patient identity</t>
         </is>
       </c>
-      <c r="F10" s="12" t="n"/>
+      <c r="F10" s="12" t="n">
+        <v>6</v>
+      </c>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="8">
         <f>IF(COUNT(G10)=0,"",IF(G10&gt;0,"YES","NO"))</f>
@@ -5074,7 +5106,9 @@
           <t>Rows corrupted (total)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
+      <c r="C14" s="12" t="n">
+        <v>249</v>
+      </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
           <t>P2 pipeline page</t>
@@ -5414,7 +5448,11 @@
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr"/>
-      <c r="F6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Nothing about real-world performance: Synthea has no typos, no interface replays, no duplicate registrations, and names carry numeric suffixes so identity matching is trivially clean. The defects are the ones I injected, so catch rate measures my checks against my own defect list, not against reality. Also learned: synthetic does not mean deterministic - the generator has a 'now' that follows the wall clock unless pinned (see #13).</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="10" t="n">
@@ -5656,7 +5694,11 @@
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
-      <c r="F17" s="13" t="inlineStr"/>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Only if every source of randomness AND every source of time is pinned. I tested it: -s alone failed four weeks later (1,151 patients, not 1,142) because Synthea's clinician seed, reference date and end date all default to the wall clock. Now -s -cs -r -e are all fixed and two runs match in content. 'Reproducible' means same content, not same bytes - the export is multi-threaded so row order varies; verify with a sorted diff or DuckDB EXCEPT, never md5. The README numbers are guaranteed by the pinned command in D2 plus the Bronze row-count check, not by a claim.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="10" t="n">

--- a/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
+++ b/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
@@ -2168,7 +2168,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr"/>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr"/>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr"/>
@@ -2312,10 +2312,14 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>D4: remediate via eAG. Range floor revised to 2.0. See validate.py dq3.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="62" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
@@ -2348,10 +2352,14 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>D7: ASOF = 2026-08-23, constant in validate.py.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="62" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
@@ -2384,7 +2392,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr"/>
@@ -2420,7 +2428,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr"/>
@@ -2456,10 +2464,14 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>Added value_text to silver_observations: 315,450 text results would otherwise be nulled by TRY_CAST.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="62" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
@@ -2492,10 +2504,14 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H37" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>6 of 6 types, 249 of 249 rows. Written to data/dq_report.json.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="62" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
@@ -2528,10 +2544,14 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H38" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>reconcile() in validate.py raises SystemExit if any table fails to balance.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
@@ -2564,7 +2584,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr"/>
@@ -4061,8 +4081,16 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr"/>
-      <c r="G8" s="13" t="inlineStr"/>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Remediate via eAG when 20 &lt; value ≤ 600 (rule A1C_MGDL_TO_PCT_EAG); quarantine everything else out of range</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>A1c of 250 is impossible as a percent but ordinary as mg/dL glucose. Converted with the ADA eAG mapping A1c = (v + 46.7) / 28.7 → 10.3 %, original kept in remediation_log, Silver row flagged 'remediated' so the correction is reversible in one WHERE clause. Quarantine was the alternative; on this extract both give 69 open gaps, so decided on principle: a logged, reversible correction beats throwing the row away for everyone. Would want clinician sign-off before running on real data.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="74" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
@@ -4156,8 +4184,16 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr"/>
-      <c r="G11" s="13" t="inlineStr"/>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Fixed as-of date 2026-08-23 (the Synthea end date), constant ASOF in validate.py</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>The data stops on 2026-08-23; no patient ever gets another A1c. A wall-clock 'today' pushes more patients past the 12-month line every day for no reason (69 gaps on the as-of date, higher every day after). Freezing today makes the report describe the data, not the calendar. Same lesson as V1.3, one layer up.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="74" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -4534,12 +4570,18 @@
       <c r="F5" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G5" s="12" t="n"/>
+      <c r="G5" s="12" t="n">
+        <v>40</v>
+      </c>
       <c r="H5" s="8">
         <f>IF(COUNT(G5)=0,"",IF(G5&gt;0,"YES","NO"))</f>
         <v/>
       </c>
-      <c r="I5" s="13" t="inlineStr"/>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Caught by its own check, all rows</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -4570,12 +4612,18 @@
       <c r="F6" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="G6" s="12" t="n"/>
+      <c r="G6" s="12" t="n">
+        <v>150</v>
+      </c>
       <c r="H6" s="8">
         <f>IF(COUNT(G6)=0,"",IF(G6&gt;0,"YES","NO"))</f>
         <v/>
       </c>
-      <c r="I6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Caught by its own check, all rows</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -4606,12 +4654,18 @@
       <c r="F7" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G7" s="12" t="n"/>
+      <c r="G7" s="12" t="n">
+        <v>20</v>
+      </c>
       <c r="H7" s="8">
         <f>IF(COUNT(G7)=0,"",IF(G7&gt;0,"YES","NO"))</f>
         <v/>
       </c>
-      <c r="I7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Caught by its own check, all rows</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -4642,12 +4696,18 @@
       <c r="F8" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="12" t="n"/>
+      <c r="G8" s="12" t="n">
+        <v>8</v>
+      </c>
       <c r="H8" s="8">
         <f>IF(COUNT(G8)=0,"",IF(G8&gt;0,"YES","NO"))</f>
         <v/>
       </c>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Caught by its own check, all rows</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
@@ -4678,12 +4738,18 @@
       <c r="F9" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G9" s="12" t="n"/>
+      <c r="G9" s="12" t="n">
+        <v>25</v>
+      </c>
       <c r="H9" s="8">
         <f>IF(COUNT(G9)=0,"",IF(G9&gt;0,"YES","NO"))</f>
         <v/>
       </c>
-      <c r="I9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Caught by its own check, all rows</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -4714,12 +4780,18 @@
       <c r="F10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="12" t="n"/>
+      <c r="G10" s="12" t="n">
+        <v>6</v>
+      </c>
       <c r="H10" s="8">
         <f>IF(COUNT(G10)=0,"",IF(G10&gt;0,"YES","NO"))</f>
         <v/>
       </c>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>Caught by its own check, all rows</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
@@ -5129,7 +5201,9 @@
           <t>Silver rows (total, all tables)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
+      <c r="C15" s="12" t="n">
+        <v>1039325</v>
+      </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
           <t>README architecture table</t>
@@ -5150,7 +5224,9 @@
           <t>Quarantined rows (total)</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr"/>
+      <c r="C16" s="12" t="n">
+        <v>223</v>
+      </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
           <t>README architecture table, P2</t>
@@ -5171,7 +5247,9 @@
           <t>Rows in identity_review</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr"/>
+      <c r="C17" s="12" t="n">
+        <v>6</v>
+      </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
           <t>P2 identity queue</t>
@@ -5192,7 +5270,9 @@
           <t>Rows in remediation_log</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr"/>
+      <c r="C18" s="12" t="n">
+        <v>20</v>
+      </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
           <t>P2 before/after example</t>
@@ -5213,7 +5293,11 @@
           <t>Catch rate</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr"/>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>6 of 6 types, 249 of 249 rows</t>
+        </is>
+      </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
           <t>README headline, P2 headline</t>

--- a/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
+++ b/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
@@ -2620,10 +2620,14 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H40" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>D5 gained 'alive on as-of': 45 of 161 are deceased. Denominator 116. D6 as written.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="62" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
@@ -2656,7 +2660,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr"/>
@@ -2692,10 +2696,14 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>Inner-join demo in day4_gold.ipynb: 116 -&gt; 95 rows, all 21 never-tested vanish = 84% of the gaps.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="62" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
@@ -2728,10 +2736,14 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H43" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>Three patients traced raw CSV -&gt; Gold in the notebook (recent / stale / never). All agree.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="62" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
@@ -2764,10 +2776,14 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H44" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>pipeline/run_all.py [--generate] [--fresh]. V4.10: 12 s from nothing, same numbers.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="62" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
@@ -2800,7 +2816,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr"/>
@@ -2836,7 +2852,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr"/>
@@ -4120,12 +4136,12 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Any of 8 diabetes SNOMED codes ever recorded. No active-as-of filter. Cohort = 161.</t>
+          <t>Any of 8 diabetes SNOMED codes ever recorded AND alive on the as-of date. Denominator = 116.</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Decided Day 1 — the evidence arrived early. Anchoring on 44054006 alone misses 73 patients who carry a diabetic complication with no underlying dx code (45% of cohort, and the sickest half). Prediabetes 714628002 excluded: 439 patients, would triple the denominator. 0 of 835 diabetes rows have a stop date, so "ever recorded" needs no date logic. See pipeline/cohort.py.</t>
+          <t>Decided Day 1 — the evidence arrived early. Anchoring on 44054006 alone misses 73 patients who carry a diabetic complication with no underlying dx code (45% of cohort, and the sickest half). Prediabetes 714628002 excluded: 439 patients, would triple the denominator. 0 of 835 diabetes rows have a stop date, so "ever recorded" needs no date logic. See pipeline/cohort.py. Day 4 added the alive clause: 45 of the 161 code-carriers died before 2026-08-23, and a care-gap list is a call list - HEDIS excludes deceased members too.</t>
         </is>
       </c>
     </row>
@@ -4155,8 +4171,16 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr"/>
-      <c r="G10" s="13" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>No A1c result (4548-4, numeric, on/before as-of) in the 365 days before as-of. Never tested = gap. &gt;365 is a gap, 365 is not.</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Ordered-but-not-resulted is not observable in Synthea (no orders table, 0 procedure rows mention A1c), so v1 counts it the same as never ordered and says so. Results in other lab systems are likewise invisible: the number is 'no result we can see'. Remediated 250s count as results (D4). Result: 25 of 116 (21.6%), 21 of them never tested - the 21 an inner join would have silently deleted.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="74" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -5319,7 +5343,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -5341,7 +5365,9 @@
           <t>Patients with an open A1c gap (numerator)</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
+      <c r="C21" s="12" t="n">
+        <v>25</v>
+      </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
           <t>README result line, P1 headline</t>
@@ -5362,7 +5388,11 @@
           <t>Gap rate %</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr"/>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
           <t>P1 headline</t>
@@ -5384,7 +5414,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
@@ -5406,7 +5436,11 @@
           <t>End-to-end pipeline runtime</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr"/>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>12 s from a deleted warehouse to Gold (run_all.py --fresh); +4 min with --generate</t>
+        </is>
+      </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Nice to quote when asked about scale</t>

--- a/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
+++ b/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
@@ -3248,10 +3248,14 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H57" s="13" t="inlineStr"/>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>Implemented from ACCESS_CONTROL.md starting matrix - still needs Franklin's revision from floor experience.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="62" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
@@ -3284,10 +3288,14 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H58" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>Static site has no request-time server, so filtering is build-time SQL: one payload per role, restricted columns never SELECTed.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="62" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
@@ -3320,10 +3328,14 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H59" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>Unit = care setting of most recent encounter (Synthea has no rostering). 70 / 106 / 116 rows.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="62" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
@@ -3356,7 +3368,7 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr"/>
@@ -3392,7 +3404,7 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr"/>
@@ -3428,10 +3440,14 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H62" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>V6.1 passes: no restricted substring appears anywhere in care_gap_pct.json.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="62" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
@@ -3464,7 +3480,7 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr"/>
@@ -4303,8 +4319,16 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr"/>
-      <c r="G14" s="13" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>PCT — the most restricted view loads first</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>The first thing a viewer sees should be a restriction, not a full table. Opening on PCT means the 12 'not available' cells are visible before anything else, which is what the page is arguing.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="74" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -4332,8 +4356,16 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr"/>
-      <c r="G15" s="13" t="inlineStr"/>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>HEDIS bands: 18-44, 45-64, 65-75, 76+</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Not round decades. The HEDIS diabetes measure applies to members 18-75 and stratifies 18-64 and 65-75, so three of the four boundaries are the measure's own. The 76+ band sits outside the measure's age range entirely - 21 of 116 patients - which is worth showing rather than hiding. Bands cover every patient (V6.8) and their gaps sum to 25 (V6.7).</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="74" customHeight="1">
       <c r="A16" s="8" t="inlineStr">

--- a/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
+++ b/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
@@ -3516,7 +3516,7 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr"/>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr"/>
@@ -3624,10 +3624,14 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H67" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>Allowlist on the statement's actual verb. A test found WITH x AS (SELECT 1) DELETE FROM patients passing - now walks the CTE list. 19/19 cases.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="62" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
@@ -3660,10 +3664,14 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H68" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>Free-text refuses anything unmatched with one sentence naming what it can answer.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="62" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
@@ -3696,10 +3704,14 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H69" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>Audit log on P4: role, question, SQL, rows, outcome. Refusals logged too.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="62" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
@@ -3732,7 +3744,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr"/>
@@ -3768,7 +3780,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr"/>
@@ -3804,10 +3816,14 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H72" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>Written from this week's real friction: DuckDB single-writer, the four-flag reproducibility failure, quarantine as a dead-letter queue.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="62" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
@@ -4393,8 +4409,16 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr"/>
-      <c r="G16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>No model. Ten preset questions with hand-written SQL, run in DuckDB-WASM in the browser.</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>D9 made the site a static export, so there is nowhere to hold an API key - a key shipped to the browser is a public key. The plan allows this cut ('ten working chips and no free-text box still demonstrates the idea') and it buys something a hosted model would not: the SQL displayed is literally the SQL executed, against the same Parquet the site ships, so a reviewer can copy it and get the same rows. The free-text box matches wording to the presets and refuses everything else by naming what it can answer. The page says it is a query builder, not a language model.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="74" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -5470,7 +5494,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>12 s from a deleted warehouse to Gold (run_all.py --fresh); +4 min with --generate</t>
+          <t>13 s warehouse-to-Gold; ~4 min with --generate (Synthea + jar download)</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">

--- a/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
+++ b/build-plan/Clinical_Care_Gap_Build_Plan.xlsx
@@ -1724,10 +1724,14 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>load_bronze.py, all_varchar=true, verified V1.5/V1.6/V1.7 on every run.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -1760,7 +1764,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr"/>
@@ -2888,7 +2892,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr"/>
@@ -2924,10 +2928,14 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>D9: static export. JSON for the pages, Parquet for DuckDB-WASM on P4.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="62" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
@@ -2960,7 +2968,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr"/>
@@ -2996,7 +3004,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr"/>
@@ -3032,7 +3040,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr"/>
@@ -3068,7 +3076,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr"/>
@@ -3104,7 +3112,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr"/>
@@ -3140,7 +3148,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr"/>
@@ -3176,7 +3184,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr"/>
@@ -3212,10 +3220,14 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H56" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>GitHub Pages (Vercel needs an interactive login). Live since Day 5.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="62" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
@@ -4277,8 +4289,16 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr"/>
-      <c r="G12" s="13" t="inlineStr"/>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>No. Quarantine is a dead-letter queue in v1; the replay path is named as scale work.</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Reprocessing needs three things this project does not have: a replay path, a resolved_at column, and a rule for whether a replayed row enters Silver under its original load date or today's. Building a half version would make the reconciliation assertion ambiguous, which is the one guarantee worth keeping exact. Written up in DATA_QUALITY_SPEC.md under what I would do differently at scale.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="74" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -4306,8 +4326,16 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr"/>
-      <c r="G13" s="13" t="inlineStr"/>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Static export at build time. JSON for the pages, Parquet for DuckDB-WASM.</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Decided Day 5, recorded here late. A server runtime holding clinical.duckdb would have failed on a serverless filesystem, and the deploy had to work on Day 5 rather than Day 7. Exporting both formats costs 458 KB: the pages render from JSON with no engine to load, and P4 queries the Parquet in the browser so the SQL it shows is the SQL that ran. The trade-off accepted is that the site reads a snapshot - re-running the pipeline without re-exporting leaves it stale, which is why export_web is the last stage of run_all.py.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="74" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
